--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
@@ -6944,7 +6944,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
@@ -4740,7 +4740,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7060,7 +7060,7 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
@@ -4740,7 +4740,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7060,7 +7060,7 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
@@ -6944,7 +6944,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
@@ -4740,7 +4740,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
@@ -4740,7 +4740,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7060,7 +7060,7 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
@@ -4740,7 +4740,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7060,7 +7060,7 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
@@ -4740,7 +4740,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
@@ -7002,7 +7002,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7060,7 +7060,7 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
@@ -6944,7 +6944,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7060,7 +7060,7 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
@@ -4740,7 +4740,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
@@ -4740,7 +4740,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7060,7 +7060,7 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,82 +417,82 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>marca</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>produto</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>quantidade</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>preco</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>site</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>data_coleta</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>preco_antigo</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>desconto</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>disponibilidade</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>produto_id</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>sku_id</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>url</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>metodo</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>medicamento_base</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>variacao</t>
         </is>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
@@ -6932,7 +6932,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
@@ -6932,7 +6932,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7048,7 +7048,7 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
@@ -4728,7 +4728,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
@@ -4728,7 +4728,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
@@ -4728,7 +4728,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7048,7 +7048,7 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
@@ -4728,7 +4728,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7048,7 +7048,7 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
@@ -4728,7 +4728,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
@@ -6932,7 +6932,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7048,7 +7048,7 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
@@ -6990,7 +6990,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7048,7 +7048,7 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
@@ -4728,7 +4728,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7048,7 +7048,7 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
@@ -6990,7 +6990,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7048,7 +7048,7 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
@@ -6932,7 +6932,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
@@ -6932,7 +6932,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7048,7 +7048,7 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
@@ -4728,7 +4728,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7048,7 +7048,7 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
@@ -4728,7 +4728,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
@@ -4728,7 +4728,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7048,7 +7048,7 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
@@ -4728,7 +4728,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7048,7 +7048,7 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
@@ -4728,7 +4728,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7048,7 +7048,7 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
@@ -4728,7 +4728,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7048,7 +7048,7 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
@@ -6932,7 +6932,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7048,7 +7048,7 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
@@ -4728,7 +4728,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7048,7 +7048,7 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
@@ -4728,7 +4728,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
@@ -4728,7 +4728,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7048,7 +7048,7 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
@@ -4728,7 +4728,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7048,7 +7048,7 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
@@ -4728,7 +4728,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20251016_201343.xlsx
@@ -4728,7 +4728,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7048,7 +7048,7 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
